--- a/data/trans_orig/P33B2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023</t>
+          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97579</t>
+          <t>95513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132505</t>
+          <t>133168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163984</t>
+          <t>165033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206834</t>
+          <t>206335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251748</t>
+          <t>249485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75273</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126876</t>
+          <t>124515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157851</t>
+          <t>157446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186431</t>
+          <t>183998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225798</t>
+          <t>225559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70027</t>
+          <t>68855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97956</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170557</t>
+          <t>170341</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205335</t>
+          <t>205081</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>248571</t>
+          <t>248927</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>296534</t>
+          <t>293544</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268119</t>
+          <t>270754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>308854</t>
+          <t>309324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>254235</t>
+          <t>256093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>295930</t>
+          <t>299366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>535123</t>
+          <t>536171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>598099</t>
+          <t>595318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74936</t>
+          <t>73716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133819</t>
+          <t>132750</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108564</t>
+          <t>110448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176914</t>
+          <t>175117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>203601</t>
+          <t>204667</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>297211</t>
+          <t>296922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93334</t>
+          <t>90216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164051</t>
+          <t>161666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156976</t>
+          <t>161073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252530</t>
+          <t>251854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>270335</t>
+          <t>279607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>397352</t>
+          <t>398802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>261795</t>
+          <t>250971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425354</t>
+          <t>429485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>468896</t>
+          <t>469680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1090947</t>
+          <t>1022215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>804040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1562490</t>
+          <t>1524712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1593970</t>
+          <t>1590652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1854903</t>
+          <t>1865850</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>904112</t>
+          <t>928529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1379896</t>
+          <t>1378312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2490487</t>
+          <t>2502783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3118907</t>
+          <t>3148504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70437</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67028</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48090</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72259</t>
+          <t>69924</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>91461</t>
+          <t>90418</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128091</t>
+          <t>128185</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160076</t>
+          <t>158515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140494</t>
+          <t>139996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176831</t>
+          <t>178628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269006</t>
+          <t>268556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>324122</t>
+          <t>323326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413300</t>
+          <t>412861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462113</t>
+          <t>463690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387533</t>
+          <t>387738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430669</t>
+          <t>429799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>815040</t>
+          <t>813995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>879367</t>
+          <t>878860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162414</t>
+          <t>157811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240308</t>
+          <t>240291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>274284</t>
+          <t>267851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>367859</t>
+          <t>368320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>470886</t>
+          <t>465694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>594731</t>
+          <t>593696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186040</t>
+          <t>194649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283581</t>
+          <t>282063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335869</t>
+          <t>339832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>461554</t>
+          <t>458427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573168</t>
+          <t>575605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>723558</t>
+          <t>722446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>456922</t>
+          <t>452976</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>653730</t>
+          <t>652667</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>814872</t>
+          <t>815881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1506020</t>
+          <t>1501089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1362970</t>
+          <t>1375285</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2149512</t>
+          <t>2197822</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2305933</t>
+          <t>2307248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2651259</t>
+          <t>2647079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1559940</t>
+          <t>1539073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2060919</t>
+          <t>2058542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3925826</t>
+          <t>3932348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4597161</t>
+          <t>4594850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>78760</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64635</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95513</t>
+          <t>100476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>148546</t>
+          <t>166895</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133168</t>
+          <t>150650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165033</t>
+          <t>185544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>227306</t>
+          <t>251091</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206335</t>
+          <t>228855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249485</t>
+          <t>275644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62785</t>
+          <t>67568</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>55287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>141225</t>
+          <t>153499</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124515</t>
+          <t>135533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157446</t>
+          <t>169852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>204010</t>
+          <t>221066</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183998</t>
+          <t>199490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225559</t>
+          <t>246028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83193</t>
+          <t>93255</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68855</t>
+          <t>78786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>109651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>187763</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170341</t>
+          <t>183204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205081</t>
+          <t>221202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270956</t>
+          <t>295094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>248927</t>
+          <t>272296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>293544</t>
+          <t>321847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>290200</t>
+          <t>333510</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270754</t>
+          <t>311186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>309324</t>
+          <t>357253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>275634</t>
+          <t>299083</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256093</t>
+          <t>277188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>299366</t>
+          <t>321771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>565835</t>
+          <t>632593</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>536171</t>
+          <t>600179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>595318</t>
+          <t>665596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106901</t>
+          <t>119231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132750</t>
+          <t>144007</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>148205</t>
+          <t>170894</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110448</t>
+          <t>148601</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>175117</t>
+          <t>194167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>255106</t>
+          <t>290125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>204667</t>
+          <t>258485</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296922</t>
+          <t>323774</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133383</t>
+          <t>140829</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90216</t>
+          <t>120173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161666</t>
+          <t>166642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>216692</t>
+          <t>243002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161073</t>
+          <t>218091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251854</t>
+          <t>268160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>350075</t>
+          <t>383831</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279607</t>
+          <t>347392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>398802</t>
+          <t>419580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>367696</t>
+          <t>406012</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250971</t>
+          <t>365513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429485</t>
+          <t>442017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>646268</t>
+          <t>490272</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469680</t>
+          <t>456902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1022215</t>
+          <t>525881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1013965</t>
+          <t>896284</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>804040</t>
+          <t>845327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524712</t>
+          <t>950550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1681316</t>
+          <t>1563413</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1590652</t>
+          <t>1516021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1865850</t>
+          <t>1610859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1226658</t>
+          <t>1267224</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>928529</t>
+          <t>1225060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1378312</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2907975</t>
+          <t>2830638</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2502783</t>
+          <t>2765021</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3148504</t>
+          <t>2893266</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289297</t>
+          <t>2229485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4527121</t>
+          <t>4400877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33874</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>50750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>56201</t>
+          <t>65168</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>51610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>82068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49638</t>
+          <t>54456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>39413</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>72503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58627</t>
+          <t>66035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>53909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69924</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>108266</t>
+          <t>120490</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>90418</t>
+          <t>101144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>136129</t>
+          <t>157854</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115231</t>
+          <t>135250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158515</t>
+          <t>181395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>158610</t>
+          <t>180783</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139996</t>
+          <t>161769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178628</t>
+          <t>204652</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>294739</t>
+          <t>338636</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268556</t>
+          <t>309133</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323326</t>
+          <t>372130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>438528</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412861</t>
+          <t>445826</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463690</t>
+          <t>501051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>409351</t>
+          <t>449333</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387738</t>
+          <t>424062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>429799</t>
+          <t>470850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>847879</t>
+          <t>922169</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813995</t>
+          <t>886671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>878860</t>
+          <t>956293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>207989</t>
+          <t>229868</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157811</t>
+          <t>201172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240291</t>
+          <t>262150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>330624</t>
+          <t>376515</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>267851</t>
+          <t>347554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>368320</t>
+          <t>410687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>538613</t>
+          <t>606384</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>465694</t>
+          <t>562103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>593696</t>
+          <t>650932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>245807</t>
+          <t>262852</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194649</t>
+          <t>233735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282063</t>
+          <t>297787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>416544</t>
+          <t>462535</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>339832</t>
+          <t>430384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>458427</t>
+          <t>499779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>662351</t>
+          <t>725388</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>575605</t>
+          <t>681246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>722446</t>
+          <t>777949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>587018</t>
+          <t>657120</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>452976</t>
+          <t>606367</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>652667</t>
+          <t>702899</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>992642</t>
+          <t>872894</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>815881</t>
+          <t>829232</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1501089</t>
+          <t>916145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1579660</t>
+          <t>1530014</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1375285</t>
+          <t>1469657</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2197822</t>
+          <t>1600634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2410045</t>
+          <t>2369760</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2307248</t>
+          <t>2311213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2647079</t>
+          <t>2431650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1911644</t>
+          <t>2015641</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1539073</t>
+          <t>1960341</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2058542</t>
+          <t>2068894</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4321690</t>
+          <t>4385400</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3932348</t>
+          <t>4303559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4594850</t>
+          <t>4466293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3450859</t>
+          <t>3519601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7102314</t>
+          <t>7247186</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7102314</t>
+          <t>7247186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7102314</t>
+          <t>7247186</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
